--- a/pipeline/credit_rating/output/xhtn_tong_hop_20260927.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20260927.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -807,7 +807,7 @@
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1229,7 +1229,7 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2653,7 +2653,7 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3219,7 +3219,7 @@
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3445,7 +3445,7 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:11</t>
+          <t>2026-09-27 14:14:04</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:11</t>
+          <t>2026-09-27 14:14:04</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:11</t>
+          <t>2026-09-27 14:14:04</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:13</t>
+          <t>2026-09-27 14:14:06</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:11</t>
+          <t>2026-09-27 14:14:04</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11325,7 +11325,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -12973,7 +12973,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13927,7 +13927,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:11</t>
+          <t>2026-09-27 14:14:04</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14833,7 +14833,7 @@
       <c r="AD126" t="inlineStr"/>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:13</t>
+          <t>2026-09-27 14:14:06</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16451,7 +16451,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16671,7 +16671,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16791,7 +16791,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16905,7 +16905,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17139,7 +17139,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:13</t>
+          <t>2026-09-27 14:14:06</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17589,7 +17589,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17817,7 +17817,7 @@
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:11</t>
+          <t>2026-09-27 14:14:04</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18151,7 +18151,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18489,7 +18489,7 @@
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18745,7 +18745,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18855,7 +18855,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -19085,7 +19085,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19309,7 +19309,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19559,7 +19559,7 @@
       <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -20063,7 +20063,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20299,7 +20299,7 @@
       <c r="AD173" t="inlineStr"/>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20411,7 +20411,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20737,7 +20737,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -20981,7 +20981,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21205,7 +21205,7 @@
       </c>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21433,7 +21433,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21543,7 +21543,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21657,7 +21657,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21767,7 +21767,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21879,7 +21879,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -21995,7 +21995,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22111,7 +22111,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22335,7 +22335,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22447,7 +22447,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:13</t>
+          <t>2026-09-27 14:14:06</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22805,7 +22805,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -22927,7 +22927,7 @@
       <c r="AD196" t="inlineStr"/>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -23053,7 +23053,7 @@
       <c r="AD197" t="inlineStr"/>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23179,7 +23179,7 @@
       <c r="AD198" t="inlineStr"/>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23409,7 +23409,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23523,7 +23523,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23637,7 +23637,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23757,7 +23757,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23877,7 +23877,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -23987,7 +23987,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -24097,7 +24097,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24207,7 +24207,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24323,7 +24323,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24451,7 +24451,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24675,7 +24675,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24793,7 +24793,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:11</t>
+          <t>2026-09-27 14:14:04</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -25013,7 +25013,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25125,7 +25125,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25235,7 +25235,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25355,7 +25355,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25715,7 +25715,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25827,7 +25827,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25939,7 +25939,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -26051,7 +26051,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26167,7 +26167,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26277,7 +26277,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26397,7 +26397,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26507,7 +26507,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26627,7 +26627,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26851,7 +26851,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:11</t>
+          <t>2026-09-27 14:14:04</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -26961,7 +26961,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27071,7 +27071,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27185,7 +27185,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27295,7 +27295,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27407,7 +27407,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27517,7 +27517,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27637,7 +27637,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27749,7 +27749,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27859,7 +27859,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -27983,7 +27983,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:13</t>
+          <t>2026-09-27 14:14:06</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:13</t>
+          <t>2026-09-27 14:14:06</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28217,7 +28217,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28327,7 +28327,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28437,7 +28437,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28549,7 +28549,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28769,7 +28769,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28897,7 +28897,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -29003,7 +29003,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29115,7 +29115,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29231,7 +29231,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29347,7 +29347,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29457,7 +29457,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29567,7 +29567,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29683,7 +29683,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29799,7 +29799,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -30025,7 +30025,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30141,7 +30141,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30251,7 +30251,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30361,7 +30361,7 @@
       </c>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30571,7 +30571,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30797,7 +30797,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30909,7 +30909,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -31019,7 +31019,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31251,7 +31251,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31361,7 +31361,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31473,7 +31473,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31589,7 +31589,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31701,7 +31701,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31811,7 +31811,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31927,7 +31927,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -32037,7 +32037,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32163,7 +32163,7 @@
       <c r="AD277" t="inlineStr"/>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32291,7 +32291,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32403,7 +32403,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32503,7 +32503,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32717,7 +32717,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32831,7 +32831,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -32931,7 +32931,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33051,7 +33051,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33163,7 +33163,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33275,7 +33275,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33389,7 +33389,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33503,7 +33503,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:11</t>
+          <t>2026-09-27 14:14:04</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33617,7 +33617,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:11</t>
+          <t>2026-09-27 14:14:04</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33749,7 +33749,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -33877,7 +33877,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -34005,7 +34005,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34133,7 +34133,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34245,7 +34245,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34357,7 +34357,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34467,7 +34467,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34577,7 +34577,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34705,7 +34705,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34815,7 +34815,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -34943,7 +34943,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -35055,7 +35055,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35167,7 +35167,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35277,7 +35277,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35397,7 +35397,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35521,7 +35521,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35645,7 +35645,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35769,7 +35769,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35881,7 +35881,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -35997,7 +35997,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36109,7 +36109,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:13</t>
+          <t>2026-09-27 14:14:06</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36237,7 +36237,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:13</t>
+          <t>2026-09-27 14:14:06</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36365,7 +36365,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36477,7 +36477,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36589,7 +36589,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36699,7 +36699,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36809,7 +36809,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36925,7 +36925,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -37037,7 +37037,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37285,7 +37285,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37501,7 +37501,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37613,7 +37613,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37741,7 +37741,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37865,7 +37865,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:13</t>
+          <t>2026-09-27 14:14:06</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -37977,7 +37977,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -38087,7 +38087,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38197,7 +38197,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38307,7 +38307,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38417,7 +38417,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38537,7 +38537,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38647,7 +38647,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38757,7 +38757,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38867,7 +38867,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -38987,7 +38987,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39107,7 +39107,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39227,7 +39227,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39347,7 +39347,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39463,7 +39463,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39579,7 +39579,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39695,7 +39695,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39807,7 +39807,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39923,7 +39923,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -40043,7 +40043,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40155,7 +40155,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40271,7 +40271,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40387,7 +40387,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40619,7 +40619,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40733,7 +40733,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:11</t>
+          <t>2026-09-27 14:14:04</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40849,7 +40849,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -40965,7 +40965,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -41081,7 +41081,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41191,7 +41191,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41307,7 +41307,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41419,7 +41419,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41529,7 +41529,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41641,7 +41641,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41753,7 +41753,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41865,7 +41865,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -41985,7 +41985,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42113,7 +42113,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42233,7 +42233,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42361,7 +42361,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42473,7 +42473,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42583,7 +42583,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42693,7 +42693,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42805,7 +42805,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42917,7 +42917,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -43027,7 +43027,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43143,7 +43143,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43253,7 +43253,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43365,7 +43365,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43475,7 +43475,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43585,7 +43585,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43713,7 +43713,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43825,7 +43825,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43953,7 +43953,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -44065,7 +44065,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44175,7 +44175,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44285,7 +44285,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44395,7 +44395,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44507,7 +44507,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44617,7 +44617,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44745,7 +44745,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44857,7 +44857,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -44967,7 +44967,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45077,7 +45077,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45187,7 +45187,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45297,7 +45297,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45407,7 +45407,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45519,7 +45519,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45647,7 +45647,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45757,7 +45757,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45867,7 +45867,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45979,7 +45979,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:13</t>
+          <t>2026-09-27 14:14:06</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46089,7 +46089,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46201,7 +46201,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46329,7 +46329,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46439,7 +46439,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46661,7 +46661,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46771,7 +46771,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46881,7 +46881,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46981,7 +46981,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47091,7 +47091,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47191,7 +47191,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47301,7 +47301,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47429,7 +47429,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47539,7 +47539,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47649,7 +47649,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47759,7 +47759,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47869,7 +47869,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47979,7 +47979,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48089,7 +48089,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48199,7 +48199,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48309,7 +48309,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48437,7 +48437,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48549,7 +48549,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48649,7 +48649,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48759,7 +48759,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48873,7 +48873,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -48983,7 +48983,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49083,7 +49083,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49195,7 +49195,7 @@
       </c>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49307,7 +49307,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49417,7 +49417,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49529,7 +49529,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49641,7 +49641,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49751,7 +49751,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49879,7 +49879,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -50011,7 +50011,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50143,7 +50143,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50275,7 +50275,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50399,7 +50399,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:13</t>
+          <t>2026-09-27 14:14:06</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50511,7 +50511,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50611,7 +50611,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50731,7 +50731,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50847,7 +50847,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -50959,7 +50959,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -51081,7 +51081,7 @@
       <c r="AD442" t="inlineStr"/>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51193,7 +51193,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51303,7 +51303,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51523,7 +51523,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51633,7 +51633,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51761,7 +51761,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51877,7 +51877,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -51987,7 +51987,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52115,7 +52115,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52243,7 +52243,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52371,7 +52371,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52499,7 +52499,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52611,7 +52611,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52721,7 +52721,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52849,7 +52849,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -52961,7 +52961,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -53073,7 +53073,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53189,7 +53189,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53301,7 +53301,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53413,7 +53413,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53525,7 +53525,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53637,7 +53637,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53757,7 +53757,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53867,7 +53867,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53995,7 +53995,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54115,7 +54115,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54227,7 +54227,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54339,7 +54339,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54439,7 +54439,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54555,7 +54555,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54665,7 +54665,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54777,7 +54777,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54887,7 +54887,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -54999,7 +54999,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55111,7 +55111,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55211,7 +55211,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55321,7 +55321,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55433,7 +55433,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55543,7 +55543,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55653,7 +55653,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55765,7 +55765,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55875,7 +55875,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -55985,7 +55985,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56095,7 +56095,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56215,7 +56215,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56339,7 +56339,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:13</t>
+          <t>2026-09-27 14:14:06</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56449,7 +56449,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56561,7 +56561,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56671,7 +56671,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56783,7 +56783,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56895,7 +56895,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -57005,7 +57005,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57115,7 +57115,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57225,7 +57225,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57335,7 +57335,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57445,7 +57445,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57555,7 +57555,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57667,7 +57667,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57779,7 +57779,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57891,7 +57891,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -58001,7 +58001,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58113,7 +58113,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58213,7 +58213,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58323,7 +58323,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58423,7 +58423,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58523,7 +58523,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58635,7 +58635,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58747,7 +58747,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58859,7 +58859,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -58969,7 +58969,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59079,7 +59079,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59189,7 +59189,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59301,7 +59301,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59411,7 +59411,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59521,7 +59521,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59631,7 +59631,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59741,7 +59741,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59853,7 +59853,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -59965,7 +59965,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60081,7 +60081,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60209,7 +60209,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60321,7 +60321,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60431,7 +60431,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60551,7 +60551,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60661,7 +60661,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60771,7 +60771,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60881,7 +60881,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -61001,7 +61001,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61117,7 +61117,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61229,7 +61229,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61349,7 +61349,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61461,7 +61461,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61561,7 +61561,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61681,7 +61681,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61791,7 +61791,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61903,7 +61903,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -62019,7 +62019,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62131,7 +62131,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62243,7 +62243,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62371,7 +62371,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62481,7 +62481,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62591,7 +62591,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62701,7 +62701,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62813,7 +62813,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62941,7 +62941,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -63053,7 +63053,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63165,7 +63165,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63277,7 +63277,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63377,7 +63377,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63487,7 +63487,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63597,7 +63597,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63697,7 +63697,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63807,7 +63807,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63935,7 +63935,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64045,7 +64045,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64157,7 +64157,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64267,7 +64267,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64379,7 +64379,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64489,7 +64489,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64599,7 +64599,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64699,7 +64699,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64809,7 +64809,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64921,7 +64921,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -65031,7 +65031,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65141,7 +65141,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65251,7 +65251,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65361,7 +65361,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65471,7 +65471,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65581,7 +65581,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65681,7 +65681,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65791,7 +65791,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65901,7 +65901,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -66013,7 +66013,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66123,7 +66123,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66235,7 +66235,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66345,7 +66345,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66455,7 +66455,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66565,7 +66565,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66675,7 +66675,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66785,7 +66785,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66897,7 +66897,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -67007,7 +67007,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67119,7 +67119,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67231,7 +67231,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67341,7 +67341,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67453,7 +67453,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67565,7 +67565,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67675,7 +67675,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67785,7 +67785,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67895,7 +67895,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -68005,7 +68005,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68105,7 +68105,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68217,7 +68217,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68327,7 +68327,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68437,7 +68437,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68565,7 +68565,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68677,7 +68677,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68789,7 +68789,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68917,7 +68917,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -69029,7 +69029,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69157,7 +69157,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69285,7 +69285,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:02</t>
+          <t>2026-09-27 14:13:53</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69397,7 +69397,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69509,7 +69509,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69619,7 +69619,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69731,7 +69731,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69841,7 +69841,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69951,7 +69951,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -70063,7 +70063,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70175,7 +70175,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70287,7 +70287,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70397,7 +70397,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70507,7 +70507,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70619,7 +70619,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70731,7 +70731,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70841,7 +70841,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70953,7 +70953,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71063,7 +71063,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71163,7 +71163,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71273,7 +71273,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71385,7 +71385,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71495,7 +71495,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71607,7 +71607,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71717,7 +71717,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71827,7 +71827,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71937,7 +71937,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72047,7 +72047,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72157,7 +72157,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72269,7 +72269,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72379,7 +72379,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72489,7 +72489,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72599,7 +72599,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72711,7 +72711,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72821,7 +72821,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72933,7 +72933,7 @@
       </c>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73045,7 +73045,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73145,7 +73145,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73255,7 +73255,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73367,7 +73367,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73479,7 +73479,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73591,7 +73591,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73703,7 +73703,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73813,7 +73813,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73923,7 +73923,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -74035,7 +74035,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74145,7 +74145,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74257,7 +74257,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74357,7 +74357,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74467,7 +74467,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74579,7 +74579,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74689,7 +74689,7 @@
       <c r="AD653" t="inlineStr"/>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:29</t>
+          <t>2026-09-27 14:14:19</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74801,7 +74801,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74913,7 +74913,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -75023,7 +75023,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75135,7 +75135,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75235,7 +75235,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75335,7 +75335,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75435,7 +75435,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75547,7 +75547,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75647,7 +75647,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75757,7 +75757,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75857,7 +75857,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -75969,7 +75969,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76081,7 +76081,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76193,7 +76193,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76305,7 +76305,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76405,7 +76405,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76517,7 +76517,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76627,7 +76627,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76739,7 +76739,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76839,7 +76839,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76939,7 +76939,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77039,7 +77039,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77139,7 +77139,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77251,7 +77251,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77363,7 +77363,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77463,7 +77463,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77573,7 +77573,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77685,7 +77685,7 @@
       </c>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77797,7 +77797,7 @@
       </c>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77909,7 +77909,7 @@
       </c>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -78021,7 +78021,7 @@
       </c>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">
@@ -78133,7 +78133,7 @@
       </c>
       <c r="AE685" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF685" t="inlineStr">
@@ -78245,7 +78245,7 @@
       </c>
       <c r="AE686" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF686" t="inlineStr">
@@ -78357,7 +78357,7 @@
       </c>
       <c r="AE687" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF687" t="inlineStr">
@@ -78457,7 +78457,7 @@
       </c>
       <c r="AE688" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF688" t="inlineStr">
@@ -78557,7 +78557,7 @@
       </c>
       <c r="AE689" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF689" t="inlineStr">
@@ -78669,7 +78669,7 @@
       </c>
       <c r="AE690" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:58</t>
+          <t>2026-09-27 14:13:47</t>
         </is>
       </c>
       <c r="AF690" t="inlineStr">
@@ -78769,7 +78769,7 @@
       </c>
       <c r="AE691" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF691" t="inlineStr">
@@ -78869,7 +78869,7 @@
       </c>
       <c r="AE692" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF692" t="inlineStr">
@@ -78969,7 +78969,7 @@
       </c>
       <c r="AE693" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF693" t="inlineStr">
@@ -79079,7 +79079,7 @@
       </c>
       <c r="AE694" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF694" t="inlineStr">
@@ -79179,7 +79179,7 @@
       </c>
       <c r="AE695" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF695" t="inlineStr">
@@ -79289,7 +79289,7 @@
       </c>
       <c r="AE696" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF696" t="inlineStr">
@@ -79371,7 +79371,7 @@
       <c r="AD697" t="inlineStr"/>
       <c r="AE697" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF697" t="inlineStr">
@@ -79453,7 +79453,7 @@
       <c r="AD698" t="inlineStr"/>
       <c r="AE698" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF698" t="inlineStr">
@@ -79535,7 +79535,7 @@
       <c r="AD699" t="inlineStr"/>
       <c r="AE699" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF699" t="inlineStr">
@@ -79617,7 +79617,7 @@
       <c r="AD700" t="inlineStr"/>
       <c r="AE700" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:06</t>
+          <t>2026-09-27 14:13:58</t>
         </is>
       </c>
       <c r="AF700" t="inlineStr">
